--- a/hong-4zzl/Hong_My_Expressions.xlsx
+++ b/hong-4zzl/Hong_My_Expressions.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="My Expressions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'My Expressions'!$A$1:$D$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'My Expressions'!$A$1:$D$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1533,7 +1533,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Four Airlines</t>
+          <t>Class 8</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -1543,19 +1543,19 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>A personality</t>
+          <t>stay calm and focused</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>에미레이트가 공고 첫 줄에 쓴 말이에요.</t>
+          <t>침착하게 집중을 유지하다</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Four Airlines</t>
+          <t>Class 8</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -1565,15 +1565,19 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>years old</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr"/>
+          <t>work closely with my team</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>팀과 긴밀히 협력하다</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Four Airlines</t>
+          <t>Class 8</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -1583,19 +1587,19 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Six lines.</t>
+          <t>many more visitors than usual</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>카타르 공식 필수 자격은 여섯 줄이에요.</t>
+          <t>평소보다 훨씬 많은 방문객</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Four Airlines</t>
+          <t>Class 8</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -1605,19 +1609,19 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Four months</t>
+          <t>at the same time</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>싱가포르항공 훈련은 4개월이에요.</t>
+          <t>동시에</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Four Airlines</t>
+          <t>Class 8</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -1627,19 +1631,19 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>and one more.</t>
+          <t>a height restriction</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>캐세이는 아시아 언어 하나를 함께 요구해요. (홍콩 베이스 공고 기준)</t>
+          <t>키 제한</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Four Airlines</t>
+          <t>Class 8</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -1649,19 +1653,19 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>TOEIC R·L</t>
+          <t>understand the customer's underlying needs</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>각 325↑ 면 영어평가 면제</t>
+          <t>고객의 진짜 필요를 이해하다</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Four Airlines</t>
+          <t>Class 8</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -1671,15 +1675,19 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>cm Not stated</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr"/>
+          <t>the sudden change to their plans</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>계획의 갑작스러운 변경</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Four Airlines</t>
+          <t>Class 8</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -1689,39 +1697,339 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Say It in English</t>
+          <t>find alternative attractions</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>예상과 달랐던 조건은 뭐였어요?</t>
+          <t>대체할 놀거리를 찾아주다</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>Class 8</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>면접·자기 PR</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>accept card payments only</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>카드 결제만 받다</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Class 8</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>면접·자기 PR</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>kindness can come back to you</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>친절은 돌아온다</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Class 8</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>면접·자기 PR</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>give first aid</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>응급처치를 하다</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Class 8</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>면접·자기 PR</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>right away</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>곧바로</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Class 8</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>면접·자기 PR</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>put up safety signs</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>안전 표지판을 세우다</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Class 8</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>면접·자기 PR</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>help the child stay calm</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>아이를 진정시키다</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
           <t>Four Airlines</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>면접·자기 PR</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>면접·자기 PR</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>A personality</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>에미레이트가 공고 첫 줄에 쓴 말이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Four Airlines</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>면접·자기 PR</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>years old</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Four Airlines</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>면접·자기 PR</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Six lines.</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>카타르 공식 필수 자격은 여섯 줄이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Four Airlines</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>면접·자기 PR</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Four months</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>싱가포르항공 훈련은 4개월이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Four Airlines</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>면접·자기 PR</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>and one more.</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>캐세이는 아시아 언어 하나를 함께 요구해요. (홍콩 베이스 공고 기준)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Four Airlines</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>면접·자기 PR</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>TOEIC R·L</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>각 325↑ 면 영어평가 면제</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Four Airlines</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>면접·자기 PR</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>cm Not stated</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Four Airlines</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>면접·자기 PR</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Say It in English</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>예상과 달랐던 조건은 뭐였어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Four Airlines</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>면접·자기 PR</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>Then again, better</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>머릿속으로 구조만 잡아요</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D69"/>
+  <autoFilter ref="A1:D83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>